--- a/cmd/res/excel/config.xlsx
+++ b/cmd/res/excel/config.xlsx
@@ -1,184 +1,311 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myshare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89225BA-B932-4F7F-BDF7-93D162AD8138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587805E8-151B-483D-A9DD-BB58E2D2C934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="point_table" sheetId="1" r:id="rId1"/>
-    <sheet name="dictionary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="72">
   <si>
     <t>标准类型</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>0618</t>
+  </si>
+  <si>
+    <t>000</t>
+  </si>
+  <si>
+    <t>浮点型</t>
+  </si>
+  <si>
+    <t>国网标准</t>
+  </si>
+  <si>
     <t>所属版本</t>
-  </si>
-  <si>
-    <t>参量特征(3bit)</t>
-  </si>
-  <si>
-    <t>参量类型编码(11bit)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参量特征(3位二进制)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参量类型编码(11位二进制)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>参量名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据长度(Byte)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>数据类型</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>数据长度(Byte)</t>
-  </si>
-  <si>
-    <t>枚举映射</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>南网标准</t>
-  </si>
-  <si>
-    <t>0618</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国网标准</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁芯接地电流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变压器铁芯
+/夹件接地
+电流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池电压</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>℃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传感器自检状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>\</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁芯-HY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁芯-通用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>长度</t>
-  </si>
-  <si>
-    <t>浮点型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10min 平均
+风速</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m/s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>微气象-通用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10min 平均
+风向</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>整型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>°（度）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大风速</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>气温</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湿度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>%RH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>气压</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hPa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 分钟降雨
+量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日照强度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>W/m2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温湿度-友讯达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电压</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>友讯达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水位-友讯达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>m</t>
-  </si>
-  <si>
-    <t>国网标准</t>
-  </si>
-  <si>
-    <t>0531</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>数据采集时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>无符号整型</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>100001</t>
-  </si>
-  <si>
-    <t>电源状态</t>
-  </si>
-  <si>
-    <t>枚举型</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>1=正常;2=异常</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>100110</t>
-  </si>
-  <si>
-    <t>均衡度</t>
-  </si>
-  <si>
-    <t>整型</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>字段</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>枚举：国网标准 / 南网标准</t>
-  </si>
-  <si>
-    <t>字符串，如 0618 / 0531</t>
-  </si>
-  <si>
-    <t>必须是3位二进制（左补0），如 000, 011</t>
-  </si>
-  <si>
-    <t>建议为11位二进制字符串（左补0）；也可写十进制，解析器会归一化为二进制</t>
-  </si>
-  <si>
-    <t>参数中文名，如 长度 / 电源状态</t>
-  </si>
-  <si>
-    <t>可选：浮点型, 整型, 无符号整型, 枚举型, 字符串</t>
-  </si>
-  <si>
-    <t>自由文本，如 m, s, %, /（无单位可用 / 或留空）</t>
-  </si>
-  <si>
-    <t>字节数，如 浮点型=4, 整型=2, 枚举=1 等；与协议打包长度保持一致</t>
-  </si>
-  <si>
-    <t>仅枚举型使用，用分号分隔，如 0=关;1=开 或 1=正常;2=异常</t>
-  </si>
-  <si>
-    <t>倍率(Scale)/偏移(Offset)</t>
-  </si>
-  <si>
-    <t>数值型；最终值 = 原始值 * 倍率 + 偏移</t>
-  </si>
-  <si>
-    <t>最小值/最大值</t>
-  </si>
-  <si>
-    <t>可选的约束；用于校验</t>
-  </si>
-  <si>
-    <t>任意说明信息</t>
-  </si>
-  <si>
-    <t>所属版本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>参量特征(3位二进制)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>参量类型编码(11位二进制)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、正常；2、异常；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10100011</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -250,13 +377,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -273,6 +407,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1009650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="文本框 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B4EA5FF-9170-B421-58F2-3237B08A231E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2495550" y="438150"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,281 +754,602 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.125" customWidth="1"/>
     <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
       <c r="H4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="H5">
-        <v>2</v>
+      <c r="F7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>